--- a/db/tablas_procesadas/Profesor.xlsx
+++ b/db/tablas_procesadas/Profesor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB7B831-F466-4FDE-91A4-A6A898351646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980B351E-2A1D-4C91-91DC-1786178256BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10710" yWindow="7365" windowWidth="28785" windowHeight="15345" xr2:uid="{5C1DD6D8-1001-4079-A3F5-95F5066F8827}"/>
+    <workbookView xWindow="8655" yWindow="4170" windowWidth="28785" windowHeight="15345" xr2:uid="{5C1DD6D8-1001-4079-A3F5-95F5066F8827}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>profesor_id</t>
   </si>
@@ -244,13 +244,16 @@
   </si>
   <si>
     <t>Kevin Torrico</t>
+  </si>
+  <si>
+    <t>count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,14 +263,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -293,9 +288,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -611,14 +605,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEB3F61-3CD2-4EA9-9987-88BCF4DAF5E1}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,8 +625,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -645,8 +642,11 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -659,8 +659,11 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -673,8 +676,11 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -687,8 +693,11 @@
       <c r="D5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -701,22 +710,28 @@
       <c r="D6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -729,8 +744,11 @@
       <c r="D8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -743,8 +761,11 @@
       <c r="D9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -757,8 +778,11 @@
       <c r="D10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -771,8 +795,11 @@
       <c r="D11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -785,8 +812,11 @@
       <c r="D12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -799,8 +829,11 @@
       <c r="D13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -813,8 +846,11 @@
       <c r="D14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -827,8 +863,11 @@
       <c r="D15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -841,8 +880,11 @@
       <c r="D16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -855,8 +897,11 @@
       <c r="D17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -869,8 +914,11 @@
       <c r="D18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -883,8 +931,11 @@
       <c r="D19" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -897,8 +948,11 @@
       <c r="D20" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -911,8 +965,11 @@
       <c r="D21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -925,8 +982,11 @@
       <c r="D22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -939,8 +999,11 @@
       <c r="D23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -953,8 +1016,11 @@
       <c r="D24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -967,8 +1033,11 @@
       <c r="D25" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -981,8 +1050,11 @@
       <c r="D26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -995,8 +1067,11 @@
       <c r="D27" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1009,8 +1084,11 @@
       <c r="D28" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1022,6 +1100,9 @@
       </c>
       <c r="D29" t="s">
         <v>3</v>
+      </c>
+      <c r="E29">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/db/tablas_procesadas/Profesor.xlsx
+++ b/db/tablas_procesadas/Profesor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980B351E-2A1D-4C91-91DC-1786178256BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A048573-AA0A-4907-8D27-5E3DD64F7CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8655" yWindow="4170" windowWidth="28785" windowHeight="15345" xr2:uid="{5C1DD6D8-1001-4079-A3F5-95F5066F8827}"/>
+    <workbookView xWindow="7365" yWindow="2760" windowWidth="28785" windowHeight="15345" xr2:uid="{5C1DD6D8-1001-4079-A3F5-95F5066F8827}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
-  <si>
-    <t>profesor_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="75">
   <si>
     <t>nombre</t>
   </si>
@@ -246,7 +243,22 @@
     <t>Kevin Torrico</t>
   </si>
   <si>
-    <t>count</t>
+    <t>id_profesor</t>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>4-5 profesores</t>
+  </si>
+  <si>
+    <t>Todas</t>
+  </si>
+  <si>
+    <t>Variado</t>
+  </si>
+  <si>
+    <t>pos_prof</t>
   </si>
 </sst>
 </file>
@@ -605,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEB3F61-3CD2-4EA9-9987-88BCF4DAF5E1}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
@@ -614,33 +626,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -648,16 +660,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -665,16 +677,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -682,16 +694,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -699,16 +711,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -716,16 +728,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -733,16 +745,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -750,16 +762,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -767,16 +779,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -784,16 +796,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -801,16 +813,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -818,16 +830,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>11</v>
@@ -835,16 +847,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>12</v>
@@ -852,16 +864,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>13</v>
@@ -869,16 +881,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -886,16 +898,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -903,16 +915,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>16</v>
@@ -920,16 +932,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>17</v>
@@ -937,16 +949,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>18</v>
@@ -954,16 +966,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>19</v>
@@ -971,16 +983,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>20</v>
@@ -988,16 +1000,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>21</v>
@@ -1005,16 +1017,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>22</v>
@@ -1022,16 +1034,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>23</v>
@@ -1039,16 +1051,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>24</v>
@@ -1056,16 +1068,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -1073,16 +1085,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <v>26</v>
@@ -1090,19 +1102,36 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
